--- a/liste groupe 3.xlsx
+++ b/liste groupe 3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEEBFEA8-C14E-447D-8EC9-02E9369AAD2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56FDE3F0-2C4C-4B6E-A973-60E0DA1BCAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 3.xlsx
+++ b/liste groupe 3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56FDE3F0-2C4C-4B6E-A973-60E0DA1BCAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844D24E2-DE1E-42D7-84CD-DA327D618E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 3.xlsx
+++ b/liste groupe 3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844D24E2-DE1E-42D7-84CD-DA327D618E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961D15C6-97B9-475B-99AF-DFF8D5BD4A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 3.xlsx
+++ b/liste groupe 3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961D15C6-97B9-475B-99AF-DFF8D5BD4A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5B3D9A-7F9A-41DF-B573-EAFE23972DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 3.xlsx
+++ b/liste groupe 3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5B3D9A-7F9A-41DF-B573-EAFE23972DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{784C2568-EFDD-48BB-9B6C-A07AF5496F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 3.xlsx
+++ b/liste groupe 3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{784C2568-EFDD-48BB-9B6C-A07AF5496F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA88167C-72B8-4C9B-B953-1B84890F8AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 3.xlsx
+++ b/liste groupe 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA88167C-72B8-4C9B-B953-1B84890F8AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C4FEF92-6FBD-4CEB-8041-3326FE628C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6960" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
